--- a/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_d_otrasrel_a_2022_nuble.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_d_otrasrel_a_2022_nuble.xlsx
@@ -141,7 +141,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-18 14:43</t>
+    <t xml:space="preserve">2026-09-24 01:33</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -579,10 +579,10 @@
         <v>0.17</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>-0.2</v>
+        <v>-0.22</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>0.37</v>
+        <v>0.39</v>
       </c>
     </row>
     <row r="3">
@@ -602,10 +602,10 @@
         <v>0.2</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>-0.26</v>
+        <v>-0.29</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>0.46</v>
+        <v>0.48</v>
       </c>
     </row>
     <row r="4">
@@ -625,10 +625,10 @@
         <v>0.33</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>-0.23</v>
+        <v>-0.25</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>0.56</v>
+        <v>0.57</v>
       </c>
     </row>
     <row r="5">
@@ -648,10 +648,10 @@
         <v>-0.25</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>-0.36</v>
+        <v>-0.37</v>
       </c>
     </row>
     <row r="6">
@@ -671,10 +671,10 @@
         <v>-0.26</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>0.18</v>
+        <v>0.2</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>-0.45</v>
+        <v>-0.46</v>
       </c>
     </row>
     <row r="7">
@@ -717,7 +717,7 @@
         <v>0.28</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>0.06</v>
+        <v>0.07</v>
       </c>
       <c r="G8" s="2" t="n">
         <v>0.22</v>
@@ -763,7 +763,7 @@
         <v>-0.11</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="G10" s="2" t="n">
         <v>-0.16</v>
@@ -812,7 +812,7 @@
         <v>0.14</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>-0.13</v>
+        <v>-0.12</v>
       </c>
     </row>
     <row r="13">
@@ -855,10 +855,10 @@
         <v>0.25</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>-0.05</v>
+        <v>-0.09</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>0.3</v>
+        <v>0.34</v>
       </c>
     </row>
     <row r="15">
@@ -878,10 +878,10 @@
         <v>0.1</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>-0.01</v>
+        <v>0.01</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>0.11</v>
+        <v>0.09</v>
       </c>
     </row>
     <row r="16">
@@ -970,7 +970,7 @@
         <v>-0.09</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>-0.17</v>
+        <v>-0.16</v>
       </c>
       <c r="G19" s="2" t="n">
         <v>0.07</v>
@@ -993,10 +993,10 @@
         <v>-0.1</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>-0.33</v>
+        <v>-0.32</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>0.23</v>
+        <v>0.22</v>
       </c>
     </row>
     <row r="21">
@@ -1013,13 +1013,13 @@
         <v>33</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>-0.26</v>
+        <v>-0.17</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>-0.02</v>
+        <v>-0.17</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>-0.24</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -1036,13 +1036,13 @@
         <v>33</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>0.35</v>
+        <v>0.3</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>-0.06</v>
+        <v>-0.13</v>
       </c>
       <c r="G22" s="2" t="n">
-        <v>0.41</v>
+        <v>0.43</v>
       </c>
     </row>
     <row r="23">
@@ -1059,13 +1059,13 @@
         <v>33</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>-0.14</v>
+        <v>-0.22</v>
       </c>
       <c r="F23" s="2" t="n">
         <v>0.14</v>
       </c>
       <c r="G23" s="2" t="n">
-        <v>-0.27</v>
+        <v>-0.36</v>
       </c>
     </row>
     <row r="24">
@@ -1085,10 +1085,10 @@
         <v>-0.47</v>
       </c>
       <c r="F24" s="2" t="n">
-        <v>-0.32</v>
+        <v>-0.33</v>
       </c>
       <c r="G24" s="2" t="n">
-        <v>-0.15</v>
+        <v>-0.14</v>
       </c>
     </row>
     <row r="25">
@@ -1108,7 +1108,7 @@
         <v>-0.75</v>
       </c>
       <c r="F25" s="2" t="n">
-        <v>-0.49</v>
+        <v>-0.5</v>
       </c>
       <c r="G25" s="2" t="n">
         <v>-0.26</v>
@@ -1131,10 +1131,10 @@
         <v>-0.46</v>
       </c>
       <c r="F26" s="2" t="n">
-        <v>-0.25</v>
+        <v>-0.27</v>
       </c>
       <c r="G26" s="2" t="n">
-        <v>-0.21</v>
+        <v>-0.2</v>
       </c>
     </row>
     <row r="27">
@@ -1154,10 +1154,10 @@
         <v>0.37</v>
       </c>
       <c r="F27" s="2" t="n">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="G27" s="2" t="n">
-        <v>0.04</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="28">
@@ -1177,10 +1177,10 @@
         <v>0.46</v>
       </c>
       <c r="F28" s="2" t="n">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="G28" s="2" t="n">
-        <v>0.03</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="29">
@@ -1223,7 +1223,7 @@
         <v>-0.31</v>
       </c>
       <c r="F30" s="2" t="n">
-        <v>-0.17</v>
+        <v>-0.18</v>
       </c>
       <c r="G30" s="2" t="n">
         <v>-0.14</v>
@@ -1315,10 +1315,10 @@
         <v>-0.25</v>
       </c>
       <c r="F34" s="2" t="n">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="G34" s="2" t="n">
-        <v>-0.43</v>
+        <v>-0.44</v>
       </c>
     </row>
     <row r="35">
@@ -1361,10 +1361,10 @@
         <v>0.38</v>
       </c>
       <c r="F36" s="2" t="n">
-        <v>0.16</v>
+        <v>0.13</v>
       </c>
       <c r="G36" s="2" t="n">
-        <v>0.22</v>
+        <v>0.24</v>
       </c>
     </row>
     <row r="37">
@@ -1384,10 +1384,10 @@
         <v>-0.1</v>
       </c>
       <c r="F37" s="2" t="n">
-        <v>-0.01</v>
+        <v>0</v>
       </c>
       <c r="G37" s="2" t="n">
-        <v>-0.09</v>
+        <v>-0.1</v>
       </c>
     </row>
     <row r="38">
@@ -1433,7 +1433,7 @@
         <v>-0.25</v>
       </c>
       <c r="G39" s="2" t="n">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="40">
@@ -1519,13 +1519,13 @@
         <v>33</v>
       </c>
       <c r="E43" s="2" t="n">
-        <v>0.52</v>
+        <v>-0.43</v>
       </c>
       <c r="F43" s="2" t="n">
-        <v>0.31</v>
+        <v>0.2</v>
       </c>
       <c r="G43" s="2" t="n">
-        <v>0.21</v>
+        <v>-0.63</v>
       </c>
     </row>
     <row r="44">
@@ -1542,13 +1542,13 @@
         <v>33</v>
       </c>
       <c r="E44" s="2" t="n">
-        <v>-0.58</v>
+        <v>-0.54</v>
       </c>
       <c r="F44" s="2" t="n">
-        <v>-0.19</v>
+        <v>-0.2</v>
       </c>
       <c r="G44" s="2" t="n">
-        <v>-0.4</v>
+        <v>-0.34</v>
       </c>
     </row>
     <row r="45">
@@ -1565,13 +1565,13 @@
         <v>33</v>
       </c>
       <c r="E45" s="2" t="n">
-        <v>0.35</v>
+        <v>-0.48</v>
       </c>
       <c r="F45" s="2" t="n">
-        <v>0.13</v>
+        <v>0.11</v>
       </c>
       <c r="G45" s="2" t="n">
-        <v>0.22</v>
+        <v>-0.6</v>
       </c>
     </row>
     <row r="46">
@@ -2025,13 +2025,13 @@
         <v>33</v>
       </c>
       <c r="E65" s="2" t="n">
-        <v>-0.62</v>
+        <v>0.54</v>
       </c>
       <c r="F65" s="2" t="n">
-        <v>-0.22</v>
+        <v>-0.18</v>
       </c>
       <c r="G65" s="2" t="n">
-        <v>-0.4</v>
+        <v>0.72</v>
       </c>
     </row>
     <row r="66">
@@ -2048,13 +2048,13 @@
         <v>33</v>
       </c>
       <c r="E66" s="2" t="n">
-        <v>0.7</v>
+        <v>0.65</v>
       </c>
       <c r="F66" s="2" t="n">
-        <v>0.31</v>
+        <v>0.33</v>
       </c>
       <c r="G66" s="2" t="n">
-        <v>0.4</v>
+        <v>0.33</v>
       </c>
     </row>
     <row r="67">
@@ -2071,13 +2071,13 @@
         <v>33</v>
       </c>
       <c r="E67" s="2" t="n">
-        <v>-0.4</v>
+        <v>0.45</v>
       </c>
       <c r="F67" s="2" t="n">
-        <v>-0.1</v>
+        <v>-0.13</v>
       </c>
       <c r="G67" s="2" t="n">
-        <v>-0.29</v>
+        <v>0.58</v>
       </c>
     </row>
   </sheetData>

--- a/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_d_otrasrel_a_2022_nuble.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_d_otrasrel_a_2022_nuble.xlsx
@@ -120,7 +120,7 @@
     <t xml:space="preserve">Migración</t>
   </si>
   <si>
-    <t xml:space="preserve">Movilidad interna (CMI)</t>
+    <t xml:space="preserve">Movilidad interna comunal (CMI)</t>
   </si>
   <si>
     <t xml:space="preserve">Saldo migratorio</t>
@@ -141,7 +141,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-24 01:33</t>
+    <t xml:space="preserve">2026-10-01 23:20</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_d_otrasrel_a_2022_nuble.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_d_otrasrel_a_2022_nuble.xlsx
@@ -141,7 +141,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-01 23:20</t>
+    <t xml:space="preserve">2026-10-05 19:58</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
